--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.42598355079718</v>
+        <v>11.93172232700454</v>
       </c>
       <c r="D2" t="n">
-        <v>73.39738536037294</v>
+        <v>11.9270751210606</v>
       </c>
       <c r="E2" t="n">
-        <v>5.881801327820044</v>
+        <v>0.9557927157707576</v>
       </c>
       <c r="F2" t="n">
-        <v>5.862501517125422</v>
+        <v>0.9526564965328805</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.86631093466767</v>
+        <v>10.3782755268835</v>
       </c>
       <c r="D3" t="n">
-        <v>63.83083666185516</v>
+        <v>10.37251095755146</v>
       </c>
       <c r="E3" t="n">
-        <v>5.881801327820044</v>
+        <v>0.9557927157707576</v>
       </c>
       <c r="F3" t="n">
-        <v>5.862501517125422</v>
+        <v>0.9526564965328805</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.56950605417512</v>
+        <v>10.33004473380346</v>
       </c>
       <c r="D4" t="n">
-        <v>63.61245123914739</v>
+        <v>10.33702332636145</v>
       </c>
       <c r="E4" t="n">
-        <v>5.881801327820044</v>
+        <v>0.9557927157707576</v>
       </c>
       <c r="F4" t="n">
-        <v>5.862501517125422</v>
+        <v>0.9526564965328805</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.19832120708914</v>
+        <v>8.969727196151984</v>
       </c>
       <c r="D5" t="n">
-        <v>55.23990265766968</v>
+        <v>8.976484181871324</v>
       </c>
       <c r="E5" t="n">
-        <v>5.881801327820044</v>
+        <v>0.9557927157707576</v>
       </c>
       <c r="F5" t="n">
-        <v>5.862501517125422</v>
+        <v>0.9526564965328805</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.85600841063298</v>
+        <v>10.86410136672786</v>
       </c>
       <c r="D6" t="n">
-        <v>66.89618204794355</v>
+        <v>10.87062958279083</v>
       </c>
       <c r="E6" t="n">
-        <v>5.881801327820044</v>
+        <v>0.9557927157707576</v>
       </c>
       <c r="F6" t="n">
-        <v>5.862501517125422</v>
+        <v>0.9526564965328805</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
